--- a/static/data/exports/Retro_KL_AE_2026.xlsx
+++ b/static/data/exports/Retro_KL_AE_2026.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E4" t="n">
         <v>21212</v>
@@ -728,7 +728,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E21" t="n">
         <v>74063</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E33" t="n">
         <v>78678</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E40" t="n">
         <v>69153</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E44" t="n">
         <v>81428</v>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E51" t="n">
         <v>78788</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E68" t="n">
         <v>64951</v>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -6626,7 +6626,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E85" t="n">
         <v>85614</v>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E91" t="n">
         <v>69743</v>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E109" t="n">
         <v>81456</v>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -8974,7 +8974,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E117" t="n">
         <v>61687</v>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -9861,7 +9861,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E129" t="n">
         <v>66882</v>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E133" t="n">
         <v>62339</v>
@@ -10769,7 +10769,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -12284,7 +12284,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E162" t="n">
         <v>77275</v>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -13308,7 +13308,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E176" t="n">
         <v>67843</v>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E184" t="n">
         <v>76342</v>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -14094,20 +14094,20 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1960151</v>
+        <v>1960152</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Akhil Kumar .a.m</t>
+          <t>Fathimathu Ruksana. P</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>26403</v>
+        <v>19702</v>
       </c>
       <c r="E187" t="n">
         <v>151</v>
@@ -14131,26 +14131,26 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Akhil Kumar .a.m</t>
+          <t>Fathimathu Ruksana. P</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>CPIM</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P187" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="Q187" t="b">
         <v>0</v>
@@ -14169,20 +14169,20 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1960152</v>
+        <v>1960151</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Fathimathu Ruksana. P</t>
+          <t>Akhil Kumar .a.m</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CPIM</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>19702</v>
+        <v>26403</v>
       </c>
       <c r="E188" t="n">
         <v>151</v>
@@ -14206,26 +14206,26 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Fathimathu Ruksana. P</t>
+          <t>Akhil Kumar .a.m</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CPIM</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P188" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="Q188" t="b">
         <v>0</v>
@@ -14291,7 +14291,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E195" t="n">
         <v>77824</v>
@@ -15103,7 +15103,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -15178,7 +15178,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -15253,7 +15253,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -15690,7 +15690,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -15806,7 +15806,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E210" t="n">
         <v>49153</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -16202,7 +16202,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -16502,7 +16502,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -16577,7 +16577,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -16830,7 +16830,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E224" t="n">
         <v>81849</v>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -17888,7 +17888,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
@@ -18038,7 +18038,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
@@ -18113,7 +18113,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
@@ -18263,7 +18263,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
@@ -18338,7 +18338,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
@@ -18413,7 +18413,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -18550,7 +18550,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
@@ -18625,7 +18625,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
@@ -18700,7 +18700,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
@@ -18775,7 +18775,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
@@ -18850,7 +18850,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
@@ -19075,7 +19075,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
@@ -19150,7 +19150,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
@@ -19225,7 +19225,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
@@ -19341,7 +19341,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E258" t="n">
         <v>70399</v>
@@ -19375,7 +19375,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
@@ -19525,7 +19525,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -19662,7 +19662,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
@@ -19812,7 +19812,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
@@ -19928,7 +19928,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E266" t="n">
         <v>58980</v>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -20686,7 +20686,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
@@ -20911,7 +20911,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O279" t="inlineStr">
@@ -20986,7 +20986,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
@@ -21123,7 +21123,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
@@ -21239,7 +21239,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E284" t="n">
         <v>73135</v>
@@ -21560,7 +21560,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
@@ -21710,7 +21710,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
@@ -21847,7 +21847,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
@@ -21922,7 +21922,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
@@ -21997,7 +21997,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
@@ -22038,7 +22038,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E295" t="n">
         <v>72457</v>
@@ -22072,7 +22072,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
@@ -22147,7 +22147,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
@@ -22284,7 +22284,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
@@ -22584,7 +22584,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
@@ -22659,7 +22659,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
@@ -22734,7 +22734,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
@@ -22809,7 +22809,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
@@ -23021,7 +23021,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
@@ -23171,7 +23171,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
@@ -23246,7 +23246,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
@@ -23321,7 +23321,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
@@ -23458,7 +23458,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
@@ -23533,7 +23533,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
@@ -23683,7 +23683,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
@@ -23758,7 +23758,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
@@ -23833,7 +23833,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
@@ -23970,7 +23970,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
@@ -24045,7 +24045,7 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O322" t="inlineStr">
@@ -24120,7 +24120,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
@@ -24195,7 +24195,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
@@ -24270,7 +24270,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
@@ -24345,7 +24345,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O326" t="inlineStr">
@@ -24420,7 +24420,7 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
@@ -24495,7 +24495,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O328" t="inlineStr">
@@ -24632,7 +24632,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
@@ -24707,7 +24707,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
@@ -24782,7 +24782,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
@@ -24857,7 +24857,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O333" t="inlineStr">
@@ -24932,7 +24932,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
@@ -25069,7 +25069,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
@@ -25219,7 +25219,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
@@ -25294,7 +25294,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
@@ -25431,7 +25431,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
@@ -25506,7 +25506,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
@@ -25581,7 +25581,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
@@ -25656,7 +25656,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
@@ -25697,7 +25697,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E345" t="n">
         <v>81971</v>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
@@ -25806,7 +25806,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
@@ -25943,7 +25943,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
@@ -26018,7 +26018,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
@@ -26093,7 +26093,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
@@ -26168,7 +26168,7 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O351" t="inlineStr">
@@ -26243,7 +26243,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
@@ -26318,7 +26318,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
@@ -26393,7 +26393,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
@@ -26434,7 +26434,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E355" t="n">
         <v>55473</v>
@@ -26468,7 +26468,7 @@
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
@@ -26618,7 +26618,7 @@
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O357" t="inlineStr">
@@ -26755,7 +26755,7 @@
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
@@ -26830,7 +26830,7 @@
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
@@ -26905,7 +26905,7 @@
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O361" t="inlineStr">
@@ -26980,7 +26980,7 @@
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O362" t="inlineStr">
@@ -27055,7 +27055,7 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
@@ -27130,7 +27130,7 @@
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O364" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O366" t="inlineStr">
@@ -27342,7 +27342,7 @@
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O367" t="inlineStr">
@@ -27383,7 +27383,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E368" t="n">
         <v>67407</v>
@@ -27417,7 +27417,7 @@
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O368" t="inlineStr">
@@ -27492,7 +27492,7 @@
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O369" t="inlineStr">
@@ -27567,7 +27567,7 @@
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O370" t="inlineStr">
@@ -27704,7 +27704,7 @@
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O372" t="inlineStr">
@@ -27779,7 +27779,7 @@
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O373" t="inlineStr">
@@ -27854,7 +27854,7 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O374" t="inlineStr">
@@ -27929,7 +27929,7 @@
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O375" t="inlineStr">
@@ -28004,7 +28004,7 @@
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O376" t="inlineStr">
@@ -28045,7 +28045,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E377" t="n">
         <v>68042</v>
@@ -28079,7 +28079,7 @@
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O377" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="N378" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O378" t="inlineStr">
@@ -28229,7 +28229,7 @@
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O379" t="inlineStr">
@@ -28366,7 +28366,7 @@
       </c>
       <c r="N381" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O381" t="inlineStr">
@@ -28441,7 +28441,7 @@
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O382" t="inlineStr">
@@ -28516,7 +28516,7 @@
       </c>
       <c r="N383" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O383" t="inlineStr">
@@ -28591,7 +28591,7 @@
       </c>
       <c r="N384" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O384" t="inlineStr">
@@ -28666,7 +28666,7 @@
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O385" t="inlineStr">
@@ -28741,7 +28741,7 @@
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O386" t="inlineStr">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O387" t="inlineStr">
@@ -28891,7 +28891,7 @@
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O388" t="inlineStr">
@@ -28966,7 +28966,7 @@
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O389" t="inlineStr">
@@ -29103,7 +29103,7 @@
       </c>
       <c r="N391" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O391" t="inlineStr">
@@ -29178,7 +29178,7 @@
       </c>
       <c r="N392" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O392" t="inlineStr">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="N393" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O393" t="inlineStr">
@@ -29294,7 +29294,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E394" t="n">
         <v>70583</v>
@@ -29328,7 +29328,7 @@
       </c>
       <c r="N394" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O394" t="inlineStr">
@@ -29403,7 +29403,7 @@
       </c>
       <c r="N395" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O395" t="inlineStr">
@@ -29478,7 +29478,7 @@
       </c>
       <c r="N396" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O396" t="inlineStr">
@@ -29553,7 +29553,7 @@
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O397" t="inlineStr">
@@ -29656,7 +29656,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E399" t="n">
         <v>75362</v>
@@ -29690,7 +29690,7 @@
       </c>
       <c r="N399" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O399" t="inlineStr">
@@ -29765,7 +29765,7 @@
       </c>
       <c r="N400" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O400" t="inlineStr">
@@ -29840,7 +29840,7 @@
       </c>
       <c r="N401" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O401" t="inlineStr">
@@ -29977,7 +29977,7 @@
       </c>
       <c r="N403" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O403" t="inlineStr">
@@ -30127,7 +30127,7 @@
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O405" t="inlineStr">
@@ -30243,7 +30243,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E407" t="n">
         <v>59028</v>
@@ -30564,7 +30564,7 @@
       </c>
       <c r="N411" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O411" t="inlineStr">
@@ -30639,7 +30639,7 @@
       </c>
       <c r="N412" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O412" t="inlineStr">
@@ -30714,7 +30714,7 @@
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O413" t="inlineStr">
@@ -30851,7 +30851,7 @@
       </c>
       <c r="N415" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O415" t="inlineStr">
@@ -30926,7 +30926,7 @@
       </c>
       <c r="N416" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O416" t="inlineStr">
@@ -31001,7 +31001,7 @@
       </c>
       <c r="N417" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O417" t="inlineStr">
@@ -31076,7 +31076,7 @@
       </c>
       <c r="N418" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O418" t="inlineStr">
@@ -31117,7 +31117,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E419" t="n">
         <v>68629</v>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="N419" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O419" t="inlineStr">
@@ -31226,7 +31226,7 @@
       </c>
       <c r="N420" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O420" t="inlineStr">
@@ -31301,7 +31301,7 @@
       </c>
       <c r="N421" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O421" t="inlineStr">
@@ -31438,7 +31438,7 @@
       </c>
       <c r="N423" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O423" t="inlineStr">
@@ -31513,7 +31513,7 @@
       </c>
       <c r="N424" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O424" t="inlineStr">
@@ -31588,7 +31588,7 @@
       </c>
       <c r="N425" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O425" t="inlineStr">
@@ -31663,7 +31663,7 @@
       </c>
       <c r="N426" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O426" t="inlineStr">
@@ -31738,7 +31738,7 @@
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O427" t="inlineStr">
@@ -31813,7 +31813,7 @@
       </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O428" t="inlineStr">
@@ -31950,7 +31950,7 @@
       </c>
       <c r="N430" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O430" t="inlineStr">
@@ -32100,7 +32100,7 @@
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O432" t="inlineStr">
@@ -32175,7 +32175,7 @@
       </c>
       <c r="N433" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O433" t="inlineStr">
@@ -32216,7 +32216,7 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E434" t="n">
         <v>60557</v>
@@ -32612,7 +32612,7 @@
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O439" t="inlineStr">
@@ -32687,7 +32687,7 @@
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O440" t="inlineStr">
@@ -32762,7 +32762,7 @@
       </c>
       <c r="N441" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O441" t="inlineStr">
@@ -32837,7 +32837,7 @@
       </c>
       <c r="N442" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O442" t="inlineStr">
@@ -32974,7 +32974,7 @@
       </c>
       <c r="N444" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O444" t="inlineStr">
@@ -33049,7 +33049,7 @@
       </c>
       <c r="N445" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O445" t="inlineStr">
@@ -33090,7 +33090,7 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E446" t="n">
         <v>66521</v>
@@ -33124,7 +33124,7 @@
       </c>
       <c r="N446" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O446" t="inlineStr">
@@ -33199,7 +33199,7 @@
       </c>
       <c r="N447" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O447" t="inlineStr">
@@ -33274,7 +33274,7 @@
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O448" t="inlineStr">
@@ -33411,7 +33411,7 @@
       </c>
       <c r="N450" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O450" t="inlineStr">
@@ -33486,7 +33486,7 @@
       </c>
       <c r="N451" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O451" t="inlineStr">
@@ -33561,7 +33561,7 @@
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O452" t="inlineStr">
@@ -33602,7 +33602,7 @@
         </is>
       </c>
       <c r="D453" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E453" t="n">
         <v>61564</v>
@@ -33636,7 +33636,7 @@
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O453" t="inlineStr">
@@ -33711,7 +33711,7 @@
       </c>
       <c r="N454" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O454" t="inlineStr">
@@ -33786,7 +33786,7 @@
       </c>
       <c r="N455" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O455" t="inlineStr">
@@ -34039,7 +34039,7 @@
         </is>
       </c>
       <c r="D459" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E459" t="n">
         <v>76073</v>
@@ -34476,7 +34476,7 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E465" t="n">
         <v>69522</v>
@@ -34510,7 +34510,7 @@
       </c>
       <c r="N465" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O465" t="inlineStr">
@@ -34585,7 +34585,7 @@
       </c>
       <c r="N466" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O466" t="inlineStr">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="N467" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O467" t="inlineStr">
@@ -34797,7 +34797,7 @@
       </c>
       <c r="N469" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O469" t="inlineStr">
@@ -34838,7 +34838,7 @@
         </is>
       </c>
       <c r="D470" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E470" t="n">
         <v>66069</v>
@@ -34872,7 +34872,7 @@
       </c>
       <c r="N470" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O470" t="inlineStr">
@@ -34947,7 +34947,7 @@
       </c>
       <c r="N471" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O471" t="inlineStr">
@@ -35022,7 +35022,7 @@
       </c>
       <c r="N472" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O472" t="inlineStr">
@@ -35097,7 +35097,7 @@
       </c>
       <c r="N473" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O473" t="inlineStr">
@@ -35234,7 +35234,7 @@
       </c>
       <c r="N475" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O475" t="inlineStr">
@@ -35309,7 +35309,7 @@
       </c>
       <c r="N476" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O476" t="inlineStr">
@@ -35350,7 +35350,7 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E477" t="n">
         <v>65337</v>
@@ -35384,7 +35384,7 @@
       </c>
       <c r="N477" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O477" t="inlineStr">
@@ -35459,7 +35459,7 @@
       </c>
       <c r="N478" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O478" t="inlineStr">
@@ -35534,7 +35534,7 @@
       </c>
       <c r="N479" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O479" t="inlineStr">
@@ -35609,7 +35609,7 @@
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O480" t="inlineStr">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="N482" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O482" t="inlineStr">
@@ -35821,7 +35821,7 @@
       </c>
       <c r="N483" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O483" t="inlineStr">
@@ -35896,7 +35896,7 @@
       </c>
       <c r="N484" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O484" t="inlineStr">
@@ -35971,7 +35971,7 @@
       </c>
       <c r="N485" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O485" t="inlineStr">
@@ -36046,7 +36046,7 @@
       </c>
       <c r="N486" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O486" t="inlineStr">
@@ -36162,7 +36162,7 @@
         </is>
       </c>
       <c r="D488" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E488" t="n">
         <v>70725</v>
@@ -36196,7 +36196,7 @@
       </c>
       <c r="N488" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O488" t="inlineStr">
@@ -36271,7 +36271,7 @@
       </c>
       <c r="N489" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O489" t="inlineStr">
@@ -36346,7 +36346,7 @@
       </c>
       <c r="N490" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O490" t="inlineStr">
@@ -36483,7 +36483,7 @@
       </c>
       <c r="N492" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O492" t="inlineStr">
@@ -36633,7 +36633,7 @@
       </c>
       <c r="N494" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O494" t="inlineStr">
@@ -36708,7 +36708,7 @@
       </c>
       <c r="N495" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O495" t="inlineStr">
@@ -36783,7 +36783,7 @@
       </c>
       <c r="N496" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O496" t="inlineStr">
@@ -36920,7 +36920,7 @@
       </c>
       <c r="N498" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O498" t="inlineStr">
@@ -36995,7 +36995,7 @@
       </c>
       <c r="N499" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O499" t="inlineStr">
@@ -37070,7 +37070,7 @@
       </c>
       <c r="N500" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O500" t="inlineStr">
@@ -37145,7 +37145,7 @@
       </c>
       <c r="N501" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O501" t="inlineStr">
@@ -37220,7 +37220,7 @@
       </c>
       <c r="N502" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O502" t="inlineStr">
@@ -37357,7 +37357,7 @@
       </c>
       <c r="N504" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O504" t="inlineStr">
@@ -37432,7 +37432,7 @@
       </c>
       <c r="N505" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O505" t="inlineStr">
@@ -37507,7 +37507,7 @@
       </c>
       <c r="N506" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O506" t="inlineStr">
@@ -37582,7 +37582,7 @@
       </c>
       <c r="N507" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O507" t="inlineStr">
@@ -37944,7 +37944,7 @@
       </c>
       <c r="N512" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O512" t="inlineStr">
@@ -38019,7 +38019,7 @@
       </c>
       <c r="N513" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O513" t="inlineStr">
@@ -38094,7 +38094,7 @@
       </c>
       <c r="N514" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O514" t="inlineStr">
@@ -38231,7 +38231,7 @@
       </c>
       <c r="N516" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O516" t="inlineStr">
@@ -38306,7 +38306,7 @@
       </c>
       <c r="N517" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O517" t="inlineStr">
@@ -38456,7 +38456,7 @@
       </c>
       <c r="N519" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O519" t="inlineStr">
@@ -38497,7 +38497,7 @@
         </is>
       </c>
       <c r="D520" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E520" t="n">
         <v>56070</v>
@@ -38531,7 +38531,7 @@
       </c>
       <c r="N520" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O520" t="inlineStr">
@@ -38606,7 +38606,7 @@
       </c>
       <c r="N521" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O521" t="inlineStr">
@@ -38818,7 +38818,7 @@
       </c>
       <c r="N524" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O524" t="inlineStr">
@@ -38893,7 +38893,7 @@
       </c>
       <c r="N525" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O525" t="inlineStr">
@@ -39009,7 +39009,7 @@
         </is>
       </c>
       <c r="D527" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E527" t="n">
         <v>63136</v>
@@ -39043,7 +39043,7 @@
       </c>
       <c r="N527" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O527" t="inlineStr">
@@ -39118,7 +39118,7 @@
       </c>
       <c r="N528" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O528" t="inlineStr">
@@ -39193,7 +39193,7 @@
       </c>
       <c r="N529" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O529" t="inlineStr">
@@ -39330,7 +39330,7 @@
       </c>
       <c r="N531" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O531" t="inlineStr">
@@ -39480,7 +39480,7 @@
       </c>
       <c r="N533" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O533" t="inlineStr">
@@ -39555,7 +39555,7 @@
       </c>
       <c r="N534" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O534" t="inlineStr">
@@ -39630,7 +39630,7 @@
       </c>
       <c r="N535" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O535" t="inlineStr">
@@ -39705,7 +39705,7 @@
       </c>
       <c r="N536" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O536" t="inlineStr">
@@ -39917,7 +39917,7 @@
       </c>
       <c r="N539" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O539" t="inlineStr">
@@ -39992,7 +39992,7 @@
       </c>
       <c r="N540" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O540" t="inlineStr">
@@ -40067,7 +40067,7 @@
       </c>
       <c r="N541" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O541" t="inlineStr">
@@ -40142,7 +40142,7 @@
       </c>
       <c r="N542" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O542" t="inlineStr">
@@ -40217,7 +40217,7 @@
       </c>
       <c r="N543" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O543" t="inlineStr">
@@ -40292,7 +40292,7 @@
       </c>
       <c r="N544" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O544" t="inlineStr">
@@ -40504,7 +40504,7 @@
       </c>
       <c r="N547" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O547" t="inlineStr">
@@ -40579,7 +40579,7 @@
       </c>
       <c r="N548" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O548" t="inlineStr">
@@ -40654,7 +40654,7 @@
       </c>
       <c r="N549" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O549" t="inlineStr">
@@ -40729,7 +40729,7 @@
       </c>
       <c r="N550" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O550" t="inlineStr">
@@ -40804,7 +40804,7 @@
       </c>
       <c r="N551" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O551" t="inlineStr">
@@ -40879,7 +40879,7 @@
       </c>
       <c r="N552" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O552" t="inlineStr">
@@ -41091,7 +41091,7 @@
       </c>
       <c r="N555" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O555" t="inlineStr">
@@ -41166,7 +41166,7 @@
       </c>
       <c r="N556" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O556" t="inlineStr">
@@ -41207,7 +41207,7 @@
         </is>
       </c>
       <c r="D557" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E557" t="n">
         <v>41323</v>
@@ -41241,7 +41241,7 @@
       </c>
       <c r="N557" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O557" t="inlineStr">
@@ -41316,7 +41316,7 @@
       </c>
       <c r="N558" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O558" t="inlineStr">
@@ -41528,7 +41528,7 @@
       </c>
       <c r="N561" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O561" t="inlineStr">
@@ -41603,7 +41603,7 @@
       </c>
       <c r="N562" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O562" t="inlineStr">
@@ -41753,7 +41753,7 @@
       </c>
       <c r="N564" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O564" t="inlineStr">
@@ -41794,7 +41794,7 @@
         </is>
       </c>
       <c r="D565" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E565" t="n">
         <v>54756</v>
@@ -41828,7 +41828,7 @@
       </c>
       <c r="N565" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O565" t="inlineStr">
@@ -41903,7 +41903,7 @@
       </c>
       <c r="N566" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O566" t="inlineStr">
@@ -42040,7 +42040,7 @@
       </c>
       <c r="N568" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O568" t="inlineStr">
@@ -42115,7 +42115,7 @@
       </c>
       <c r="N569" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O569" t="inlineStr">
@@ -42156,7 +42156,7 @@
         </is>
       </c>
       <c r="D570" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E570" t="n">
         <v>64294</v>
@@ -42190,7 +42190,7 @@
       </c>
       <c r="N570" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O570" t="inlineStr">
@@ -42265,7 +42265,7 @@
       </c>
       <c r="N571" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O571" t="inlineStr">
@@ -42340,7 +42340,7 @@
       </c>
       <c r="N572" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O572" t="inlineStr">
@@ -42477,7 +42477,7 @@
       </c>
       <c r="N574" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O574" t="inlineStr">
@@ -42552,7 +42552,7 @@
       </c>
       <c r="N575" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O575" t="inlineStr">
@@ -42627,7 +42627,7 @@
       </c>
       <c r="N576" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O576" t="inlineStr">
@@ -42702,7 +42702,7 @@
       </c>
       <c r="N577" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O577" t="inlineStr">
@@ -42777,7 +42777,7 @@
       </c>
       <c r="N578" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O578" t="inlineStr">
@@ -42852,7 +42852,7 @@
       </c>
       <c r="N579" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O579" t="inlineStr">
@@ -42927,7 +42927,7 @@
       </c>
       <c r="N580" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O580" t="inlineStr">
@@ -43064,7 +43064,7 @@
       </c>
       <c r="N582" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O582" t="inlineStr">
@@ -43214,7 +43214,7 @@
       </c>
       <c r="N584" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O584" t="inlineStr">
@@ -43289,7 +43289,7 @@
       </c>
       <c r="N585" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O585" t="inlineStr">
@@ -43364,7 +43364,7 @@
       </c>
       <c r="N586" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O586" t="inlineStr">
@@ -43405,7 +43405,7 @@
         </is>
       </c>
       <c r="D587" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E587" t="n">
         <v>50464</v>
@@ -43439,7 +43439,7 @@
       </c>
       <c r="N587" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O587" t="inlineStr">
@@ -43514,7 +43514,7 @@
       </c>
       <c r="N588" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O588" t="inlineStr">
@@ -43651,7 +43651,7 @@
       </c>
       <c r="N590" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O590" t="inlineStr">
@@ -43726,7 +43726,7 @@
       </c>
       <c r="N591" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O591" t="inlineStr">
@@ -43801,7 +43801,7 @@
       </c>
       <c r="N592" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O592" t="inlineStr">
@@ -43876,7 +43876,7 @@
       </c>
       <c r="N593" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O593" t="inlineStr">
@@ -43917,7 +43917,7 @@
         </is>
       </c>
       <c r="D594" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E594" t="n">
         <v>56130</v>
@@ -43951,7 +43951,7 @@
       </c>
       <c r="N594" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O594" t="inlineStr">
@@ -44026,7 +44026,7 @@
       </c>
       <c r="N595" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O595" t="inlineStr">
@@ -44163,7 +44163,7 @@
       </c>
       <c r="N597" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O597" t="inlineStr">
@@ -44238,7 +44238,7 @@
       </c>
       <c r="N598" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O598" t="inlineStr">
@@ -44313,7 +44313,7 @@
       </c>
       <c r="N599" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O599" t="inlineStr">
@@ -44354,7 +44354,7 @@
         </is>
       </c>
       <c r="D600" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E600" t="n">
         <v>51788</v>
@@ -44388,7 +44388,7 @@
       </c>
       <c r="N600" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O600" t="inlineStr">
@@ -44463,7 +44463,7 @@
       </c>
       <c r="N601" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O601" t="inlineStr">
@@ -44600,7 +44600,7 @@
       </c>
       <c r="N603" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O603" t="inlineStr">
@@ -44750,7 +44750,7 @@
       </c>
       <c r="N605" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O605" t="inlineStr">
@@ -44825,7 +44825,7 @@
       </c>
       <c r="N606" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O606" t="inlineStr">
@@ -45050,7 +45050,7 @@
       </c>
       <c r="N609" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O609" t="inlineStr">
@@ -45125,7 +45125,7 @@
       </c>
       <c r="N610" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O610" t="inlineStr">
@@ -45200,7 +45200,7 @@
       </c>
       <c r="N611" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O611" t="inlineStr">
@@ -45337,7 +45337,7 @@
       </c>
       <c r="N613" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O613" t="inlineStr">
@@ -45487,7 +45487,7 @@
       </c>
       <c r="N615" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O615" t="inlineStr">
@@ -45528,7 +45528,7 @@
         </is>
       </c>
       <c r="D616" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E616" t="n">
         <v>33164</v>
@@ -45562,7 +45562,7 @@
       </c>
       <c r="N616" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O616" t="inlineStr">
@@ -45637,7 +45637,7 @@
       </c>
       <c r="N617" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O617" t="inlineStr">
@@ -45774,7 +45774,7 @@
       </c>
       <c r="N619" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O619" t="inlineStr">
@@ -45849,7 +45849,7 @@
       </c>
       <c r="N620" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O620" t="inlineStr">
@@ -45965,7 +45965,7 @@
         </is>
       </c>
       <c r="D622" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E622" t="n">
         <v>49009</v>
@@ -46361,7 +46361,7 @@
       </c>
       <c r="N627" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O627" t="inlineStr">
@@ -46436,7 +46436,7 @@
       </c>
       <c r="N628" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O628" t="inlineStr">
@@ -46511,7 +46511,7 @@
       </c>
       <c r="N629" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O629" t="inlineStr">
@@ -46648,7 +46648,7 @@
       </c>
       <c r="N631" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O631" t="inlineStr">
@@ -46873,7 +46873,7 @@
       </c>
       <c r="N634" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O634" t="inlineStr">
@@ -46948,7 +46948,7 @@
       </c>
       <c r="N635" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O635" t="inlineStr">
@@ -47023,7 +47023,7 @@
       </c>
       <c r="N636" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O636" t="inlineStr">
@@ -47098,7 +47098,7 @@
       </c>
       <c r="N637" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O637" t="inlineStr">
@@ -47235,7 +47235,7 @@
       </c>
       <c r="N639" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O639" t="inlineStr">
@@ -47310,7 +47310,7 @@
       </c>
       <c r="N640" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O640" t="inlineStr">
@@ -47351,7 +47351,7 @@
         </is>
       </c>
       <c r="D641" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E641" t="n">
         <v>56620</v>
@@ -47385,7 +47385,7 @@
       </c>
       <c r="N641" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O641" t="inlineStr">
@@ -47460,7 +47460,7 @@
       </c>
       <c r="N642" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O642" t="inlineStr">
@@ -47535,7 +47535,7 @@
       </c>
       <c r="N643" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O643" t="inlineStr">
@@ -47672,7 +47672,7 @@
       </c>
       <c r="N645" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O645" t="inlineStr">
@@ -47747,7 +47747,7 @@
       </c>
       <c r="N646" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O646" t="inlineStr">
@@ -47822,7 +47822,7 @@
       </c>
       <c r="N647" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O647" t="inlineStr">
@@ -47938,7 +47938,7 @@
         </is>
       </c>
       <c r="D649" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E649" t="n">
         <v>45357</v>
@@ -48409,7 +48409,7 @@
       </c>
       <c r="N655" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O655" t="inlineStr">
@@ -48450,7 +48450,7 @@
         </is>
       </c>
       <c r="D656" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E656" t="n">
         <v>44895</v>
@@ -48484,7 +48484,7 @@
       </c>
       <c r="N656" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O656" t="inlineStr">
@@ -48559,7 +48559,7 @@
       </c>
       <c r="N657" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O657" t="inlineStr">
@@ -48634,7 +48634,7 @@
       </c>
       <c r="N658" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O658" t="inlineStr">
@@ -48771,7 +48771,7 @@
       </c>
       <c r="N660" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O660" t="inlineStr">
@@ -48846,7 +48846,7 @@
       </c>
       <c r="N661" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O661" t="inlineStr">
@@ -48921,7 +48921,7 @@
       </c>
       <c r="N662" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O662" t="inlineStr">
@@ -48996,7 +48996,7 @@
       </c>
       <c r="N663" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O663" t="inlineStr">
@@ -49071,7 +49071,7 @@
       </c>
       <c r="N664" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O664" t="inlineStr">
@@ -49146,7 +49146,7 @@
       </c>
       <c r="N665" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O665" t="inlineStr">
@@ -49283,7 +49283,7 @@
       </c>
       <c r="N667" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O667" t="inlineStr">
@@ -49358,7 +49358,7 @@
       </c>
       <c r="N668" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O668" t="inlineStr">
@@ -49433,7 +49433,7 @@
       </c>
       <c r="N669" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O669" t="inlineStr">
@@ -49508,7 +49508,7 @@
       </c>
       <c r="N670" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O670" t="inlineStr">
@@ -49583,7 +49583,7 @@
       </c>
       <c r="N671" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O671" t="inlineStr">
@@ -49658,7 +49658,7 @@
       </c>
       <c r="N672" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O672" t="inlineStr">
@@ -49795,7 +49795,7 @@
       </c>
       <c r="N674" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O674" t="inlineStr">
@@ -49870,7 +49870,7 @@
       </c>
       <c r="N675" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O675" t="inlineStr">
@@ -49945,7 +49945,7 @@
       </c>
       <c r="N676" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O676" t="inlineStr">
@@ -50232,7 +50232,7 @@
       </c>
       <c r="N680" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O680" t="inlineStr">
@@ -50307,7 +50307,7 @@
       </c>
       <c r="N681" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O681" t="inlineStr">
@@ -50382,7 +50382,7 @@
       </c>
       <c r="N682" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O682" t="inlineStr">
@@ -50519,7 +50519,7 @@
       </c>
       <c r="N684" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O684" t="inlineStr">
@@ -50669,7 +50669,7 @@
       </c>
       <c r="N686" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O686" t="inlineStr">
@@ -50744,7 +50744,7 @@
       </c>
       <c r="N687" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O687" t="inlineStr">
@@ -50819,7 +50819,7 @@
       </c>
       <c r="N688" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O688" t="inlineStr">
@@ -50894,7 +50894,7 @@
       </c>
       <c r="N689" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O689" t="inlineStr">
@@ -50969,7 +50969,7 @@
       </c>
       <c r="N690" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O690" t="inlineStr">
@@ -51044,7 +51044,7 @@
       </c>
       <c r="N691" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O691" t="inlineStr">
@@ -51181,7 +51181,7 @@
       </c>
       <c r="N693" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O693" t="inlineStr">
@@ -51209,11 +51209,11 @@
     </row>
     <row r="694">
       <c r="A694" t="n">
-        <v>1960659</v>
+        <v>1960658</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Indu</t>
+          <t>M.m.scaria</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -51246,7 +51246,7 @@
       </c>
       <c r="K694" t="inlineStr">
         <is>
-          <t>Indu</t>
+          <t>M.m.scaria</t>
         </is>
       </c>
       <c r="L694" t="inlineStr">
@@ -51256,16 +51256,16 @@
       </c>
       <c r="N694" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O694" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P694" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="Q694" t="b">
         <v>0</v>
@@ -51284,11 +51284,11 @@
     </row>
     <row r="695">
       <c r="A695" t="n">
-        <v>1960658</v>
+        <v>1960659</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>M.m.scaria</t>
+          <t>Indu</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -51321,7 +51321,7 @@
       </c>
       <c r="K695" t="inlineStr">
         <is>
-          <t>M.m.scaria</t>
+          <t>Indu</t>
         </is>
       </c>
       <c r="L695" t="inlineStr">
@@ -51331,16 +51331,16 @@
       </c>
       <c r="N695" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O695" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P695" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="Q695" t="b">
         <v>0</v>
@@ -51993,7 +51993,7 @@
       </c>
       <c r="N704" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O704" t="inlineStr">
@@ -52034,7 +52034,7 @@
         </is>
       </c>
       <c r="D705" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E705" t="n">
         <v>44325</v>
@@ -52068,7 +52068,7 @@
       </c>
       <c r="N705" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O705" t="inlineStr">
@@ -52143,7 +52143,7 @@
       </c>
       <c r="N706" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O706" t="inlineStr">
@@ -52280,7 +52280,7 @@
       </c>
       <c r="N708" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O708" t="inlineStr">
@@ -52430,7 +52430,7 @@
       </c>
       <c r="N710" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O710" t="inlineStr">
@@ -52505,7 +52505,7 @@
       </c>
       <c r="N711" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O711" t="inlineStr">
@@ -52546,7 +52546,7 @@
         </is>
       </c>
       <c r="D712" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E712" t="n">
         <v>32907</v>
@@ -52580,7 +52580,7 @@
       </c>
       <c r="N712" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O712" t="inlineStr">
@@ -52655,7 +52655,7 @@
       </c>
       <c r="N713" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O713" t="inlineStr">
@@ -52730,7 +52730,7 @@
       </c>
       <c r="N714" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O714" t="inlineStr">
@@ -52867,7 +52867,7 @@
       </c>
       <c r="N716" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O716" t="inlineStr">
@@ -52942,7 +52942,7 @@
       </c>
       <c r="N717" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O717" t="inlineStr">
@@ -53017,7 +53017,7 @@
       </c>
       <c r="N718" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O718" t="inlineStr">
@@ -53058,7 +53058,7 @@
         </is>
       </c>
       <c r="D719" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E719" t="n">
         <v>31124</v>
@@ -53092,7 +53092,7 @@
       </c>
       <c r="N719" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O719" t="inlineStr">
@@ -53167,7 +53167,7 @@
       </c>
       <c r="N720" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O720" t="inlineStr">
@@ -53242,7 +53242,7 @@
       </c>
       <c r="N721" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O721" t="inlineStr">
@@ -53379,7 +53379,7 @@
       </c>
       <c r="N723" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O723" t="inlineStr">
@@ -53454,7 +53454,7 @@
       </c>
       <c r="N724" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O724" t="inlineStr">
@@ -53529,7 +53529,7 @@
       </c>
       <c r="N725" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O725" t="inlineStr">
@@ -53604,7 +53604,7 @@
       </c>
       <c r="N726" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O726" t="inlineStr">
@@ -53679,7 +53679,7 @@
       </c>
       <c r="N727" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O727" t="inlineStr">
@@ -53754,7 +53754,7 @@
       </c>
       <c r="N728" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O728" t="inlineStr">
@@ -53829,7 +53829,7 @@
       </c>
       <c r="N729" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O729" t="inlineStr">
@@ -53966,7 +53966,7 @@
       </c>
       <c r="N731" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O731" t="inlineStr">
@@ -54041,7 +54041,7 @@
       </c>
       <c r="N732" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O732" t="inlineStr">
@@ -54116,7 +54116,7 @@
       </c>
       <c r="N733" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O733" t="inlineStr">
@@ -54191,7 +54191,7 @@
       </c>
       <c r="N734" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O734" t="inlineStr">
@@ -54266,7 +54266,7 @@
       </c>
       <c r="N735" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O735" t="inlineStr">
@@ -54341,7 +54341,7 @@
       </c>
       <c r="N736" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O736" t="inlineStr">
@@ -54416,7 +54416,7 @@
       </c>
       <c r="N737" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O737" t="inlineStr">
@@ -54491,7 +54491,7 @@
       </c>
       <c r="N738" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O738" t="inlineStr">
@@ -54628,7 +54628,7 @@
       </c>
       <c r="N740" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O740" t="inlineStr">
@@ -54703,7 +54703,7 @@
       </c>
       <c r="N741" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O741" t="inlineStr">
@@ -54778,7 +54778,7 @@
       </c>
       <c r="N742" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O742" t="inlineStr">
@@ -54853,7 +54853,7 @@
       </c>
       <c r="N743" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O743" t="inlineStr">
@@ -54928,7 +54928,7 @@
       </c>
       <c r="N744" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O744" t="inlineStr">
@@ -55065,7 +55065,7 @@
       </c>
       <c r="N746" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O746" t="inlineStr">
@@ -55140,7 +55140,7 @@
       </c>
       <c r="N747" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O747" t="inlineStr">
@@ -55215,7 +55215,7 @@
       </c>
       <c r="N748" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O748" t="inlineStr">
@@ -55290,7 +55290,7 @@
       </c>
       <c r="N749" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O749" t="inlineStr">
@@ -55331,7 +55331,7 @@
         </is>
       </c>
       <c r="D750" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E750" t="n">
         <v>65145</v>
@@ -55365,7 +55365,7 @@
       </c>
       <c r="N750" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O750" t="inlineStr">
@@ -55440,7 +55440,7 @@
       </c>
       <c r="N751" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O751" t="inlineStr">
@@ -55577,7 +55577,7 @@
       </c>
       <c r="N753" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O753" t="inlineStr">
@@ -55727,7 +55727,7 @@
       </c>
       <c r="N755" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O755" t="inlineStr">
@@ -55802,7 +55802,7 @@
       </c>
       <c r="N756" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O756" t="inlineStr">
@@ -55877,7 +55877,7 @@
       </c>
       <c r="N757" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O757" t="inlineStr">
@@ -55952,7 +55952,7 @@
       </c>
       <c r="N758" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O758" t="inlineStr">
@@ -56089,7 +56089,7 @@
       </c>
       <c r="N760" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O760" t="inlineStr">
@@ -56164,7 +56164,7 @@
       </c>
       <c r="N761" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O761" t="inlineStr">
@@ -56239,7 +56239,7 @@
       </c>
       <c r="N762" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O762" t="inlineStr">
@@ -56314,7 +56314,7 @@
       </c>
       <c r="N763" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O763" t="inlineStr">
@@ -56389,7 +56389,7 @@
       </c>
       <c r="N764" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O764" t="inlineStr">
@@ -56430,7 +56430,7 @@
         </is>
       </c>
       <c r="D765" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E765" t="n">
         <v>60050</v>
@@ -56464,7 +56464,7 @@
       </c>
       <c r="N765" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O765" t="inlineStr">
@@ -56539,7 +56539,7 @@
       </c>
       <c r="N766" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O766" t="inlineStr">
@@ -56676,7 +56676,7 @@
       </c>
       <c r="N768" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O768" t="inlineStr">
@@ -56826,7 +56826,7 @@
       </c>
       <c r="N770" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O770" t="inlineStr">
@@ -56901,7 +56901,7 @@
       </c>
       <c r="N771" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O771" t="inlineStr">
@@ -56942,7 +56942,7 @@
         </is>
       </c>
       <c r="D772" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E772" t="n">
         <v>47249</v>
@@ -56976,7 +56976,7 @@
       </c>
       <c r="N772" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O772" t="inlineStr">
@@ -57051,7 +57051,7 @@
       </c>
       <c r="N773" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O773" t="inlineStr">
@@ -57126,7 +57126,7 @@
       </c>
       <c r="N774" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O774" t="inlineStr">
@@ -57263,7 +57263,7 @@
       </c>
       <c r="N776" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O776" t="inlineStr">
@@ -57338,7 +57338,7 @@
       </c>
       <c r="N777" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O777" t="inlineStr">
@@ -57413,7 +57413,7 @@
       </c>
       <c r="N778" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O778" t="inlineStr">
@@ -57550,7 +57550,7 @@
       </c>
       <c r="N780" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O780" t="inlineStr">
@@ -57700,7 +57700,7 @@
       </c>
       <c r="N782" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O782" t="inlineStr">
@@ -57775,7 +57775,7 @@
       </c>
       <c r="N783" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O783" t="inlineStr">
@@ -57850,7 +57850,7 @@
       </c>
       <c r="N784" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O784" t="inlineStr">
@@ -57925,7 +57925,7 @@
       </c>
       <c r="N785" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O785" t="inlineStr">
@@ -58000,7 +58000,7 @@
       </c>
       <c r="N786" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O786" t="inlineStr">
@@ -58075,7 +58075,7 @@
       </c>
       <c r="N787" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O787" t="inlineStr">
@@ -58212,7 +58212,7 @@
       </c>
       <c r="N789" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O789" t="inlineStr">
@@ -58362,7 +58362,7 @@
       </c>
       <c r="N791" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O791" t="inlineStr">
@@ -58437,7 +58437,7 @@
       </c>
       <c r="N792" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O792" t="inlineStr">
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="D793" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E793" t="n">
         <v>61079</v>
@@ -58512,7 +58512,7 @@
       </c>
       <c r="N793" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O793" t="inlineStr">
@@ -58587,7 +58587,7 @@
       </c>
       <c r="N794" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O794" t="inlineStr">
@@ -58690,7 +58690,7 @@
         </is>
       </c>
       <c r="D796" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E796" t="n">
         <v>67180</v>
@@ -59052,7 +59052,7 @@
         </is>
       </c>
       <c r="D801" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E801" t="n">
         <v>57859</v>
@@ -59086,7 +59086,7 @@
       </c>
       <c r="N801" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O801" t="inlineStr">
@@ -59161,7 +59161,7 @@
       </c>
       <c r="N802" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O802" t="inlineStr">
@@ -59236,7 +59236,7 @@
       </c>
       <c r="N803" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O803" t="inlineStr">
@@ -59373,7 +59373,7 @@
       </c>
       <c r="N805" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O805" t="inlineStr">
@@ -59448,7 +59448,7 @@
       </c>
       <c r="N806" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O806" t="inlineStr">
@@ -59523,7 +59523,7 @@
       </c>
       <c r="N807" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O807" t="inlineStr">
@@ -59598,7 +59598,7 @@
       </c>
       <c r="N808" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O808" t="inlineStr">
@@ -59748,7 +59748,7 @@
       </c>
       <c r="N810" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O810" t="inlineStr">
@@ -59885,7 +59885,7 @@
       </c>
       <c r="N812" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O812" t="inlineStr">
@@ -59960,7 +59960,7 @@
       </c>
       <c r="N813" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O813" t="inlineStr">
@@ -60035,7 +60035,7 @@
       </c>
       <c r="N814" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O814" t="inlineStr">
@@ -60110,7 +60110,7 @@
       </c>
       <c r="N815" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O815" t="inlineStr">
@@ -60185,7 +60185,7 @@
       </c>
       <c r="N816" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O816" t="inlineStr">
@@ -60322,7 +60322,7 @@
       </c>
       <c r="N818" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O818" t="inlineStr">
@@ -60397,7 +60397,7 @@
       </c>
       <c r="N819" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O819" t="inlineStr">
@@ -60438,7 +60438,7 @@
         </is>
       </c>
       <c r="D820" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E820" t="n">
         <v>51098</v>
@@ -60472,7 +60472,7 @@
       </c>
       <c r="N820" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O820" t="inlineStr">
@@ -60547,7 +60547,7 @@
       </c>
       <c r="N821" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O821" t="inlineStr">
@@ -60759,7 +60759,7 @@
       </c>
       <c r="N824" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O824" t="inlineStr">
@@ -60875,7 +60875,7 @@
         </is>
       </c>
       <c r="D826" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E826" t="n">
         <v>60380</v>
@@ -60909,7 +60909,7 @@
       </c>
       <c r="N826" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O826" t="inlineStr">
@@ -60984,7 +60984,7 @@
       </c>
       <c r="N827" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O827" t="inlineStr">
@@ -61059,7 +61059,7 @@
       </c>
       <c r="N828" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O828" t="inlineStr">
@@ -61196,7 +61196,7 @@
       </c>
       <c r="N830" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O830" t="inlineStr">
@@ -61633,7 +61633,7 @@
       </c>
       <c r="N836" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O836" t="inlineStr">
@@ -61708,7 +61708,7 @@
       </c>
       <c r="N837" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O837" t="inlineStr">
@@ -61783,7 +61783,7 @@
       </c>
       <c r="N838" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O838" t="inlineStr">
@@ -61858,7 +61858,7 @@
       </c>
       <c r="N839" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O839" t="inlineStr">
@@ -61995,7 +61995,7 @@
       </c>
       <c r="N841" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O841" t="inlineStr">
@@ -62070,7 +62070,7 @@
       </c>
       <c r="N842" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O842" t="inlineStr">
@@ -62145,7 +62145,7 @@
       </c>
       <c r="N843" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O843" t="inlineStr">
@@ -62220,7 +62220,7 @@
       </c>
       <c r="N844" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O844" t="inlineStr">
@@ -62760,7 +62760,7 @@
         </is>
       </c>
       <c r="D852" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E852" t="n">
         <v>63926</v>
@@ -62794,7 +62794,7 @@
       </c>
       <c r="N852" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O852" t="inlineStr">
@@ -62869,7 +62869,7 @@
       </c>
       <c r="N853" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O853" t="inlineStr">
@@ -62944,7 +62944,7 @@
       </c>
       <c r="N854" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O854" t="inlineStr">
@@ -63081,7 +63081,7 @@
       </c>
       <c r="N856" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O856" t="inlineStr">
@@ -63156,7 +63156,7 @@
       </c>
       <c r="N857" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O857" t="inlineStr">
@@ -63231,7 +63231,7 @@
       </c>
       <c r="N858" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O858" t="inlineStr">
@@ -63306,7 +63306,7 @@
       </c>
       <c r="N859" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O859" t="inlineStr">
@@ -63381,7 +63381,7 @@
       </c>
       <c r="N860" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O860" t="inlineStr">
@@ -63456,7 +63456,7 @@
       </c>
       <c r="N861" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O861" t="inlineStr">
@@ -63668,7 +63668,7 @@
       </c>
       <c r="N864" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O864" t="inlineStr">
@@ -63818,7 +63818,7 @@
       </c>
       <c r="N866" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O866" t="inlineStr">
@@ -63893,7 +63893,7 @@
       </c>
       <c r="N867" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O867" t="inlineStr">
@@ -63968,7 +63968,7 @@
       </c>
       <c r="N868" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O868" t="inlineStr">
@@ -64043,7 +64043,7 @@
       </c>
       <c r="N869" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O869" t="inlineStr">
@@ -64118,7 +64118,7 @@
       </c>
       <c r="N870" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O870" t="inlineStr">
@@ -64405,7 +64405,7 @@
       </c>
       <c r="N874" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O874" t="inlineStr">
@@ -64480,7 +64480,7 @@
       </c>
       <c r="N875" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O875" t="inlineStr">
@@ -64555,7 +64555,7 @@
       </c>
       <c r="N876" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O876" t="inlineStr">
@@ -64630,7 +64630,7 @@
       </c>
       <c r="N877" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O877" t="inlineStr">
@@ -64842,7 +64842,7 @@
       </c>
       <c r="N880" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O880" t="inlineStr">
@@ -64917,7 +64917,7 @@
       </c>
       <c r="N881" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O881" t="inlineStr">
@@ -64958,7 +64958,7 @@
         </is>
       </c>
       <c r="D882" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E882" t="n">
         <v>55298</v>
@@ -64992,7 +64992,7 @@
       </c>
       <c r="N882" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O882" t="inlineStr">
@@ -65067,7 +65067,7 @@
       </c>
       <c r="N883" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O883" t="inlineStr">
@@ -65142,7 +65142,7 @@
       </c>
       <c r="N884" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O884" t="inlineStr">
@@ -65429,7 +65429,7 @@
       </c>
       <c r="N888" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O888" t="inlineStr">
@@ -65470,7 +65470,7 @@
         </is>
       </c>
       <c r="D889" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E889" t="n">
         <v>46586</v>
@@ -65504,7 +65504,7 @@
       </c>
       <c r="N889" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O889" t="inlineStr">
@@ -65579,7 +65579,7 @@
       </c>
       <c r="N890" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O890" t="inlineStr">
@@ -65716,7 +65716,7 @@
       </c>
       <c r="N892" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O892" t="inlineStr">
@@ -65866,7 +65866,7 @@
       </c>
       <c r="N894" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O894" t="inlineStr">
@@ -65907,7 +65907,7 @@
         </is>
       </c>
       <c r="D895" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E895" t="n">
         <v>55580</v>
@@ -65941,7 +65941,7 @@
       </c>
       <c r="N895" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O895" t="inlineStr">
@@ -66016,7 +66016,7 @@
       </c>
       <c r="N896" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O896" t="inlineStr">
@@ -66153,7 +66153,7 @@
       </c>
       <c r="N898" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O898" t="inlineStr">
@@ -66228,7 +66228,7 @@
       </c>
       <c r="N899" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O899" t="inlineStr">
@@ -66303,7 +66303,7 @@
       </c>
       <c r="N900" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O900" t="inlineStr">
@@ -66378,7 +66378,7 @@
       </c>
       <c r="N901" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O901" t="inlineStr">
@@ -66453,7 +66453,7 @@
       </c>
       <c r="N902" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O902" t="inlineStr">
@@ -66590,7 +66590,7 @@
       </c>
       <c r="N904" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O904" t="inlineStr">
@@ -66706,7 +66706,7 @@
         </is>
       </c>
       <c r="D906" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E906" t="n">
         <v>55365</v>
@@ -66740,7 +66740,7 @@
       </c>
       <c r="N906" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O906" t="inlineStr">
@@ -66815,7 +66815,7 @@
       </c>
       <c r="N907" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O907" t="inlineStr">
@@ -66890,7 +66890,7 @@
       </c>
       <c r="N908" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O908" t="inlineStr">
@@ -67102,7 +67102,7 @@
       </c>
       <c r="N911" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O911" t="inlineStr">
@@ -67177,7 +67177,7 @@
       </c>
       <c r="N912" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O912" t="inlineStr">
@@ -67252,7 +67252,7 @@
       </c>
       <c r="N913" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O913" t="inlineStr">
@@ -67327,7 +67327,7 @@
       </c>
       <c r="N914" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O914" t="inlineStr">
@@ -67402,7 +67402,7 @@
       </c>
       <c r="N915" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O915" t="inlineStr">
@@ -67443,7 +67443,7 @@
         </is>
       </c>
       <c r="D916" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E916" t="n">
         <v>59163</v>
@@ -68426,7 +68426,7 @@
       </c>
       <c r="N929" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O929" t="inlineStr">
@@ -68501,7 +68501,7 @@
       </c>
       <c r="N930" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O930" t="inlineStr">
@@ -68576,7 +68576,7 @@
       </c>
       <c r="N931" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O931" t="inlineStr">
@@ -68651,7 +68651,7 @@
       </c>
       <c r="N932" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O932" t="inlineStr">
@@ -69013,7 +69013,7 @@
       </c>
       <c r="N937" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O937" t="inlineStr">
@@ -69088,7 +69088,7 @@
       </c>
       <c r="N938" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O938" t="inlineStr">
@@ -69163,7 +69163,7 @@
       </c>
       <c r="N939" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O939" t="inlineStr">
@@ -69204,7 +69204,7 @@
         </is>
       </c>
       <c r="D940" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E940" t="n">
         <v>61405</v>
@@ -69238,7 +69238,7 @@
       </c>
       <c r="N940" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O940" t="inlineStr">
@@ -69313,7 +69313,7 @@
       </c>
       <c r="N941" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O941" t="inlineStr">
@@ -69600,7 +69600,7 @@
       </c>
       <c r="N945" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O945" t="inlineStr">
@@ -69675,7 +69675,7 @@
       </c>
       <c r="N946" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O946" t="inlineStr">
@@ -69716,7 +69716,7 @@
         </is>
       </c>
       <c r="D947" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E947" t="n">
         <v>46136</v>
@@ -69750,7 +69750,7 @@
       </c>
       <c r="N947" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O947" t="inlineStr">
@@ -69825,7 +69825,7 @@
       </c>
       <c r="N948" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O948" t="inlineStr">
@@ -69962,7 +69962,7 @@
       </c>
       <c r="N950" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O950" t="inlineStr">
@@ -70112,7 +70112,7 @@
       </c>
       <c r="N952" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O952" t="inlineStr">
@@ -70187,7 +70187,7 @@
       </c>
       <c r="N953" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O953" t="inlineStr">
@@ -70262,7 +70262,7 @@
       </c>
       <c r="N954" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O954" t="inlineStr">
@@ -70303,7 +70303,7 @@
         </is>
       </c>
       <c r="D955" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E955" t="n">
         <v>42913</v>
@@ -70337,7 +70337,7 @@
       </c>
       <c r="N955" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O955" t="inlineStr">
@@ -70412,7 +70412,7 @@
       </c>
       <c r="N956" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O956" t="inlineStr">
@@ -70624,7 +70624,7 @@
       </c>
       <c r="N959" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O959" t="inlineStr">
@@ -70699,7 +70699,7 @@
       </c>
       <c r="N960" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O960" t="inlineStr">
@@ -70774,7 +70774,7 @@
       </c>
       <c r="N961" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O961" t="inlineStr">
@@ -70849,7 +70849,7 @@
       </c>
       <c r="N962" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O962" t="inlineStr">
@@ -70924,7 +70924,7 @@
       </c>
       <c r="N963" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O963" t="inlineStr">
@@ -70999,7 +70999,7 @@
       </c>
       <c r="N964" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O964" t="inlineStr">
@@ -71074,7 +71074,7 @@
       </c>
       <c r="N965" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O965" t="inlineStr">
@@ -71211,7 +71211,7 @@
       </c>
       <c r="N967" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O967" t="inlineStr">
@@ -71286,7 +71286,7 @@
       </c>
       <c r="N968" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O968" t="inlineStr">
@@ -71361,7 +71361,7 @@
       </c>
       <c r="N969" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O969" t="inlineStr">
@@ -71436,7 +71436,7 @@
       </c>
       <c r="N970" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O970" t="inlineStr">
@@ -71511,7 +71511,7 @@
       </c>
       <c r="N971" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O971" t="inlineStr">
@@ -71586,7 +71586,7 @@
       </c>
       <c r="N972" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O972" t="inlineStr">
@@ -71661,7 +71661,7 @@
       </c>
       <c r="N973" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O973" t="inlineStr">
@@ -71736,7 +71736,7 @@
       </c>
       <c r="N974" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O974" t="inlineStr">
@@ -71811,7 +71811,7 @@
       </c>
       <c r="N975" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O975" t="inlineStr">
@@ -71852,7 +71852,7 @@
         </is>
       </c>
       <c r="D976" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E976" t="n">
         <v>52214</v>
@@ -71886,7 +71886,7 @@
       </c>
       <c r="N976" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O976" t="inlineStr">
@@ -71961,7 +71961,7 @@
       </c>
       <c r="N977" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O977" t="inlineStr">
@@ -72098,7 +72098,7 @@
       </c>
       <c r="N979" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O979" t="inlineStr">
@@ -72173,7 +72173,7 @@
       </c>
       <c r="N980" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O980" t="inlineStr">
@@ -72248,7 +72248,7 @@
       </c>
       <c r="N981" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O981" t="inlineStr">
@@ -72323,7 +72323,7 @@
       </c>
       <c r="N982" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O982" t="inlineStr">
@@ -72473,7 +72473,7 @@
       </c>
       <c r="N984" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O984" t="inlineStr">
@@ -72589,7 +72589,7 @@
         </is>
       </c>
       <c r="D986" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E986" t="n">
         <v>61907</v>
@@ -72623,7 +72623,7 @@
       </c>
       <c r="N986" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O986" t="inlineStr">
@@ -72698,7 +72698,7 @@
       </c>
       <c r="N987" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O987" t="inlineStr">
@@ -72773,7 +72773,7 @@
       </c>
       <c r="N988" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O988" t="inlineStr">
@@ -72985,7 +72985,7 @@
       </c>
       <c r="N991" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O991" t="inlineStr">
@@ -73060,7 +73060,7 @@
       </c>
       <c r="N992" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O992" t="inlineStr">
@@ -73135,7 +73135,7 @@
       </c>
       <c r="N993" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O993" t="inlineStr">
@@ -73176,7 +73176,7 @@
         </is>
       </c>
       <c r="D994" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E994" t="n">
         <v>69149</v>
@@ -73210,7 +73210,7 @@
       </c>
       <c r="N994" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O994" t="inlineStr">
@@ -73285,7 +73285,7 @@
       </c>
       <c r="N995" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O995" t="inlineStr">
@@ -73360,7 +73360,7 @@
       </c>
       <c r="N996" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O996" t="inlineStr">
@@ -73572,7 +73572,7 @@
       </c>
       <c r="N999" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O999" t="inlineStr">
@@ -73647,7 +73647,7 @@
       </c>
       <c r="N1000" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1000" t="inlineStr">
@@ -73722,7 +73722,7 @@
       </c>
       <c r="N1001" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1001" t="inlineStr">
@@ -73797,7 +73797,7 @@
       </c>
       <c r="N1002" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1002" t="inlineStr">
@@ -73872,7 +73872,7 @@
       </c>
       <c r="N1003" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1003" t="inlineStr">
@@ -73913,7 +73913,7 @@
         </is>
       </c>
       <c r="D1004" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E1004" t="n">
         <v>49710</v>
@@ -73947,7 +73947,7 @@
       </c>
       <c r="N1004" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1004" t="inlineStr">
@@ -74022,7 +74022,7 @@
       </c>
       <c r="N1005" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1005" t="inlineStr">
@@ -74159,7 +74159,7 @@
       </c>
       <c r="N1007" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1007" t="inlineStr">
@@ -74234,7 +74234,7 @@
       </c>
       <c r="N1008" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1008" t="inlineStr">
@@ -74309,7 +74309,7 @@
       </c>
       <c r="N1009" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1009" t="inlineStr">
@@ -74384,7 +74384,7 @@
       </c>
       <c r="N1010" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1010" t="inlineStr">
@@ -74459,7 +74459,7 @@
       </c>
       <c r="N1011" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1011" t="inlineStr">
@@ -74596,7 +74596,7 @@
       </c>
       <c r="N1013" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1013" t="inlineStr">
@@ -74671,7 +74671,7 @@
       </c>
       <c r="N1014" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1014" t="inlineStr">
@@ -74821,7 +74821,7 @@
       </c>
       <c r="N1016" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1016" t="inlineStr">
@@ -74896,7 +74896,7 @@
       </c>
       <c r="N1017" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1017" t="inlineStr">
@@ -74971,7 +74971,7 @@
       </c>
       <c r="N1018" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1018" t="inlineStr">
@@ -75046,7 +75046,7 @@
       </c>
       <c r="N1019" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1019" t="inlineStr">
@@ -75087,7 +75087,7 @@
         </is>
       </c>
       <c r="D1020" t="n">
-        <v>27582</v>
+        <v>19700</v>
       </c>
       <c r="E1020" t="n">
         <v>51794</v>
@@ -75121,7 +75121,7 @@
       </c>
       <c r="N1020" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1020" t="inlineStr">
@@ -75196,7 +75196,7 @@
       </c>
       <c r="N1021" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1021" t="inlineStr">
@@ -75333,7 +75333,7 @@
       </c>
       <c r="N1023" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1023" t="inlineStr">
@@ -75408,7 +75408,7 @@
       </c>
       <c r="N1024" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O1024" t="inlineStr">
